--- a/output/Tables/Modal shift/HIA_modal_shift_Rubin_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_Rubin_1000replicate.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>24832.721</v>
+        <v>70264.197</v>
       </c>
       <c r="C2">
-        <v>22162.019</v>
+        <v>66828.175</v>
       </c>
       <c r="D2">
-        <v>27503.422</v>
+        <v>73700.21799999999</v>
       </c>
       <c r="E2">
-        <v>261443.348</v>
+        <v>721719.487</v>
       </c>
       <c r="F2">
-        <v>246066.633</v>
+        <v>701648.311</v>
       </c>
       <c r="G2">
-        <v>276820.064</v>
+        <v>741790.662</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>34771965325.229</v>
+        <v>95988691705.438</v>
       </c>
       <c r="L2">
-        <v>32726862126.244</v>
+        <v>93319225378.605</v>
       </c>
       <c r="M2">
-        <v>36817068524.214</v>
+        <v>98658158032.271</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>14879.564</v>
+        <v>49987.962</v>
       </c>
       <c r="C3">
-        <v>13650.739</v>
+        <v>47910.422</v>
       </c>
       <c r="D3">
-        <v>16108.388</v>
+        <v>52065.502</v>
       </c>
       <c r="E3">
-        <v>13339.373</v>
+        <v>44517.872</v>
       </c>
       <c r="F3">
-        <v>12378.632</v>
+        <v>42872.975</v>
       </c>
       <c r="G3">
-        <v>14300.115</v>
+        <v>46162.769</v>
       </c>
       <c r="H3">
-        <v>828821457.075</v>
+        <v>2784429483.902</v>
       </c>
       <c r="I3">
-        <v>760373463.656</v>
+        <v>2668706349.701</v>
       </c>
       <c r="J3">
-        <v>897269450.493</v>
+        <v>2900152618.102</v>
       </c>
       <c r="K3">
-        <v>1774136659.319</v>
+        <v>5920877006.444</v>
       </c>
       <c r="L3">
-        <v>1646358028.658</v>
+        <v>5702105697.778</v>
       </c>
       <c r="M3">
-        <v>1901915289.98</v>
+        <v>6139648315.109</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>9807.367</v>
+        <v>39877.561</v>
       </c>
       <c r="C4">
-        <v>9157.112999999999</v>
+        <v>38129.83</v>
       </c>
       <c r="D4">
-        <v>10457.622</v>
+        <v>41625.292</v>
       </c>
       <c r="E4">
-        <v>15052.401</v>
+        <v>60161.544</v>
       </c>
       <c r="F4">
-        <v>13742.548</v>
+        <v>56879.905</v>
       </c>
       <c r="G4">
-        <v>16362.254</v>
+        <v>63443.183</v>
       </c>
       <c r="H4">
-        <v>145217689.674</v>
+        <v>590467046.008</v>
       </c>
       <c r="I4">
-        <v>135589377.266</v>
+        <v>564588396.247</v>
       </c>
       <c r="J4">
-        <v>154846002.083</v>
+        <v>616345695.77</v>
       </c>
       <c r="K4">
-        <v>2001969335.498</v>
+        <v>8001485412.334</v>
       </c>
       <c r="L4">
-        <v>1827758922.685</v>
+        <v>7565027429.228</v>
       </c>
       <c r="M4">
-        <v>2176179748.312</v>
+        <v>8437943395.44</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>1935.851</v>
+        <v>8147.728</v>
       </c>
       <c r="C5">
-        <v>1791.554</v>
+        <v>7780.709</v>
       </c>
       <c r="D5">
-        <v>2080.149</v>
+        <v>8514.746999999999</v>
       </c>
       <c r="E5">
-        <v>3793.103</v>
+        <v>15904.959</v>
       </c>
       <c r="F5">
-        <v>3493.597</v>
+        <v>15154.036</v>
       </c>
       <c r="G5">
-        <v>4092.609</v>
+        <v>16655.882</v>
       </c>
       <c r="H5">
-        <v>145577966.586</v>
+        <v>612717287.002</v>
       </c>
       <c r="I5">
-        <v>134726676.795</v>
+        <v>585117070.2819999</v>
       </c>
       <c r="J5">
-        <v>156429256.378</v>
+        <v>640317503.723</v>
       </c>
       <c r="K5">
-        <v>504482752.994</v>
+        <v>2115359531.81</v>
       </c>
       <c r="L5">
-        <v>464648444.373</v>
+        <v>2015486743.189</v>
       </c>
       <c r="M5">
-        <v>544317061.6160001</v>
+        <v>2215232320.43</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>5134.07</v>
+        <v>17395.1</v>
       </c>
       <c r="C6">
-        <v>4524.886</v>
+        <v>16366.987</v>
       </c>
       <c r="D6">
-        <v>5743.253</v>
+        <v>18423.213</v>
       </c>
       <c r="E6">
-        <v>8557.913</v>
+        <v>28772.754</v>
       </c>
       <c r="F6">
-        <v>7781.429</v>
+        <v>27424.701</v>
       </c>
       <c r="G6">
-        <v>9334.397000000001</v>
+        <v>30120.807</v>
       </c>
       <c r="H6">
-        <v>86452600.42</v>
+        <v>292916091.58</v>
       </c>
       <c r="I6">
-        <v>76194559.25300001</v>
+        <v>275603701.612</v>
       </c>
       <c r="J6">
-        <v>96710641.588</v>
+        <v>310228481.547</v>
       </c>
       <c r="K6">
-        <v>1138202443.431</v>
+        <v>3826776300.53</v>
       </c>
       <c r="L6">
-        <v>1034930034.252</v>
+        <v>3647485212.179</v>
       </c>
       <c r="M6">
-        <v>1241474852.611</v>
+        <v>4006067388.88</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +643,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>39969.514</v>
+        <v>159363.809</v>
       </c>
       <c r="C7">
-        <v>37590.922</v>
+        <v>153780.265</v>
       </c>
       <c r="D7">
-        <v>42348.105</v>
+        <v>164947.353</v>
       </c>
       <c r="E7">
-        <v>12938.017</v>
+        <v>51684.463</v>
       </c>
       <c r="F7">
-        <v>11832.887</v>
+        <v>49173.121</v>
       </c>
       <c r="G7">
-        <v>14043.146</v>
+        <v>54195.806</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1720756202.786</v>
+        <v>6874033644.604</v>
       </c>
       <c r="L7">
-        <v>1573774017.477</v>
+        <v>6540025147.983</v>
       </c>
       <c r="M7">
-        <v>1867738388.094</v>
+        <v>7208042141.226</v>
       </c>
     </row>
     <row r="8">
@@ -686,40 +686,40 @@
         </is>
       </c>
       <c r="B8">
-        <v>71726.36600000001</v>
+        <v>274772.16</v>
       </c>
       <c r="C8">
-        <v>66715.21400000001</v>
+        <v>263968.213</v>
       </c>
       <c r="D8">
-        <v>76737.51700000001</v>
+        <v>285576.107</v>
       </c>
       <c r="E8">
-        <v>53680.80699999999</v>
+        <v>201041.592</v>
       </c>
       <c r="F8">
-        <v>49229.09300000001</v>
+        <v>191504.738</v>
       </c>
       <c r="G8">
-        <v>58132.521</v>
+        <v>210578.447</v>
       </c>
       <c r="H8">
-        <v>1206069713.755</v>
+        <v>4280529908.492</v>
       </c>
       <c r="I8">
-        <v>1106884076.97</v>
+        <v>4094015517.842</v>
       </c>
       <c r="J8">
-        <v>1305255350.542</v>
+        <v>4467044299.142</v>
       </c>
       <c r="K8">
-        <v>7139547394.028</v>
+        <v>26738531895.722</v>
       </c>
       <c r="L8">
-        <v>6547469447.445001</v>
+        <v>25470130230.357</v>
       </c>
       <c r="M8">
-        <v>7731625340.613</v>
+        <v>28006933561.085</v>
       </c>
     </row>
     <row r="9">
@@ -729,40 +729,40 @@
         </is>
       </c>
       <c r="B9">
-        <v>96559.087</v>
+        <v>345036.357</v>
       </c>
       <c r="C9">
-        <v>88877.23300000001</v>
+        <v>330796.388</v>
       </c>
       <c r="D9">
-        <v>104240.939</v>
+        <v>359276.325</v>
       </c>
       <c r="E9">
-        <v>315124.155</v>
+        <v>922761.0789999999</v>
       </c>
       <c r="F9">
-        <v>295295.726</v>
+        <v>893153.049</v>
       </c>
       <c r="G9">
-        <v>334952.585</v>
+        <v>952369.1089999999</v>
       </c>
       <c r="H9">
-        <v>1206069713.755</v>
+        <v>4280529908.492</v>
       </c>
       <c r="I9">
-        <v>1106884076.97</v>
+        <v>4094015517.842</v>
       </c>
       <c r="J9">
-        <v>1305255350.542</v>
+        <v>4467044299.142</v>
       </c>
       <c r="K9">
-        <v>41911512719.257</v>
+        <v>122727223601.16</v>
       </c>
       <c r="L9">
-        <v>39274331573.689</v>
+        <v>118789355608.962</v>
       </c>
       <c r="M9">
-        <v>44548693864.827</v>
+        <v>126665091593.356</v>
       </c>
     </row>
   </sheetData>
